--- a/web-app/public/upload-tagihan-example.xlsx
+++ b/web-app/public/upload-tagihan-example.xlsx
@@ -1,76 +1,134 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SyrelGroup\Hasamitra\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SyrelGroup\Hasamitra\apps-hmjb\web-app\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A3B63E1-6275-42F0-9A47-B8495999AD9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7852FCDF-DB68-4224-A122-175D5B937C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="10890" xr2:uid="{D0915118-2298-4042-B17F-C83BE2A8DD7A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Loan04" sheetId="32" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Loan04!$A$1:$R$2</definedName>
+    <definedName name="INSTANSI">#REF!</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
-  <si>
-    <t>cif</t>
-  </si>
-  <si>
-    <t>nik</t>
-  </si>
-  <si>
-    <t>nama</t>
-  </si>
-  <si>
-    <t>tanggal_tagih</t>
-  </si>
-  <si>
-    <t>tanggal_tertagih</t>
-  </si>
-  <si>
-    <t>nominal_realisasi</t>
-  </si>
-  <si>
-    <t>nominal_tagihan</t>
-  </si>
-  <si>
-    <t>SALOMON SERAN</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
+  <si>
+    <t>INSTANSI</t>
+  </si>
+  <si>
+    <t>Pensiunan</t>
+  </si>
+  <si>
+    <t>POSTRA</t>
+  </si>
+  <si>
+    <t>SEGMENTASI</t>
+  </si>
+  <si>
+    <t>NOREK</t>
+  </si>
+  <si>
+    <t>NAMA</t>
+  </si>
+  <si>
+    <t>CIF</t>
+  </si>
+  <si>
+    <t>NO_IDENTITAS</t>
+  </si>
+  <si>
+    <t>KD_KOL_EFF</t>
+  </si>
+  <si>
+    <t>SLD_PINJAMAN_PKK</t>
+  </si>
+  <si>
+    <t>NILAI_FAS_ASAL</t>
+  </si>
+  <si>
+    <t>SLD_TUNGGAK_PKK</t>
+  </si>
+  <si>
+    <t>SLD_TUNGGAK_BGA</t>
+  </si>
+  <si>
+    <t>NILAI_TGH_ANGSURAN</t>
+  </si>
+  <si>
+    <t>TGL_BUKA</t>
+  </si>
+  <si>
+    <t>TGL_AKHIR_FAS</t>
+  </si>
+  <si>
+    <t>JANGKA_BLN</t>
+  </si>
+  <si>
+    <t>TGL_JTH_TMP</t>
+  </si>
+  <si>
+    <t>NAMA_AO</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>0010116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALOMON SERAN  </t>
   </si>
   <si>
     <t>5304233112500005</t>
+  </si>
+  <si>
+    <t>Lainnya</t>
+  </si>
+  <si>
+    <t>BAYAR</t>
+  </si>
+  <si>
+    <t>PARTIAL</t>
+  </si>
+  <si>
+    <t>BELUMBAYAR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="_(* #,###.##000_);_(* \(#,###.##000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,###_);_(* \(#,###\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Cambria"/>
-      <family val="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -90,24 +148,293 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="18">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <u val="none"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri Light"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="double">
+          <color rgb="FFFF0000"/>
+        </left>
+        <right style="double">
+          <color rgb="FFFF0000"/>
+        </right>
+        <top style="double">
+          <color rgb="FFFF0000"/>
+        </top>
+        <bottom style="double">
+          <color rgb="FFFF0000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </horizontal>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="3" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="17"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstColumn" dxfId="14"/>
+      <tableStyleElement type="lastColumn" dxfId="13"/>
+      <tableStyleElement type="firstRowStripe" dxfId="12"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="11"/>
+    </tableStyle>
+    <tableStyle name="Slicer Style 1" pivot="0" table="0" count="1" xr9:uid="{2BE21CEA-6445-47FC-985E-228944B59B60}">
+      <tableStyleElement type="wholeTable" dxfId="10"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1">
+        <x14:slicerStyle name="Slicer Style 1"/>
+      </x14:slicerStyles>
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
       <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
@@ -117,7 +444,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -133,7 +460,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -145,7 +472,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -159,12 +486,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -192,31 +519,14 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -244,23 +554,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -403,73 +696,259 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{442BE49C-AAFC-4C90-B2EC-CB90A04E3671}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:R4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="2" max="2" width="46.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="30.85546875" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15" customWidth="1"/>
+    <col min="11" max="11" width="20.28515625" customWidth="1"/>
+    <col min="12" max="12" width="23.42578125" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" customWidth="1"/>
+    <col min="14" max="14" width="16.140625" customWidth="1"/>
+    <col min="15" max="15" width="13.5703125" style="5" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
+    <col min="17" max="17" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:18">
+      <c r="A1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="G1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="R1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
+      <c r="A2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2">
+        <v>10011169</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" t="s">
-        <v>4</v>
+      <c r="G2" s="5">
+        <v>1</v>
+      </c>
+      <c r="H2" s="4">
+        <v>104676132.47</v>
+      </c>
+      <c r="I2" s="4">
+        <v>108500000</v>
+      </c>
+      <c r="J2" s="5">
+        <v>0</v>
+      </c>
+      <c r="K2" s="5">
+        <v>0</v>
+      </c>
+      <c r="L2" s="5">
+        <v>1884807.87</v>
+      </c>
+      <c r="M2" s="3">
+        <v>45951</v>
+      </c>
+      <c r="N2" s="3">
+        <v>48880</v>
+      </c>
+      <c r="O2" s="5">
+        <v>96</v>
+      </c>
+      <c r="P2" s="3">
+        <v>46140</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="R2" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+    <row r="3" spans="1:18">
+      <c r="A3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3">
         <v>10011169</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="4">
-        <v>2000000</v>
-      </c>
-      <c r="E2" s="4">
+      <c r="D3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="4">
+        <v>104676132.47</v>
+      </c>
+      <c r="I3" s="4">
+        <v>108500000</v>
+      </c>
+      <c r="J3" s="5">
         <v>0</v>
       </c>
-      <c r="F2" s="1">
-        <v>46144</v>
-      </c>
-      <c r="G2" s="1"/>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1884807.87</v>
+      </c>
+      <c r="M3" s="3">
+        <v>45951</v>
+      </c>
+      <c r="N3" s="3">
+        <v>48880</v>
+      </c>
+      <c r="O3" s="5">
+        <v>96</v>
+      </c>
+      <c r="P3" s="3">
+        <v>46140</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="R3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="A4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4">
+        <v>10011169</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4">
+        <v>104676132.47</v>
+      </c>
+      <c r="I4" s="4">
+        <v>108500000</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1884807.87</v>
+      </c>
+      <c r="M4" s="3">
+        <v>45951</v>
+      </c>
+      <c r="N4" s="3">
+        <v>48880</v>
+      </c>
+      <c r="O4" s="5">
+        <v>96</v>
+      </c>
+      <c r="P4" s="3">
+        <v>46140</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="R4" t="s">
+        <v>26</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>